--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_ablation_redundancy.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_ablation_redundancy.xlsx
@@ -719,7 +719,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05961396256854015</v>
+        <v>0.05961411085445417</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
